--- a/KPI.xlsx
+++ b/KPI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04DE9AFA-9F59-42FD-AF29-95DB2562A2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C8998977-3DA3-449E-AAD2-5613B1FF68E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1CF27B0E-1027-4419-BEEC-551758462B63}"/>
   </bookViews>
@@ -1078,7 +1078,349 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[KPI.xlsx]KPI!PivotTable1</c:name>
+    <c:fmtId val="12"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>KPI!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>KPI!$I$2:$I$4</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Accessories</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Electronics</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>KPI!$J$2:$J$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>30100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>371500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-075F-4CBF-83D7-211F64FDFE72}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1621,6 +1963,525 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1654,6 +2515,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57B1C345-F5F4-A00F-4F64-83C0FDADF27A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3801,7 +4698,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B1D6B85-ABC5-4AD5-BEE7-AEC5263673BC}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B1D6B85-ABC5-4AD5-BEE7-AEC5263673BC}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
   <location ref="I1:J4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -4251,6 +5148,17 @@
   <dataFields count="1">
     <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="12" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">

--- a/KPI.xlsx
+++ b/KPI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C8998977-3DA3-449E-AAD2-5613B1FF68E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7DB1FC9C-C1B3-4E57-82ED-6B4EB3BDFD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1CF27B0E-1027-4419-BEEC-551758462B63}"/>
   </bookViews>
@@ -1380,6 +1380,446 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[KPI.xlsx]KPI!PivotTable5</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>KPI!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>KPI!$L$2:$L$12</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>KPI!$M$2:$M$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>52000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>63000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>59500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13800</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>65200</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19800</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>60200</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32200</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18400</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-073D-413B-8B78-06BAD4CCCF72}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1308470191"/>
+        <c:axId val="1308470671"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1308470191"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1308470671"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1308470671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1308470191"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1460,6 +1900,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -2450,6 +2930,522 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2551,6 +3547,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EC9EB41-41AD-1273-1047-75C71F14D90E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3213,7 +4245,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A45B3224-92A1-441B-B04F-0B4385BE255C}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A45B3224-92A1-441B-B04F-0B4385BE255C}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="L1:M12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -3696,6 +4728,17 @@
   <dataFields count="1">
     <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">

--- a/KPI.xlsx
+++ b/KPI.xlsx
@@ -8,22 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7DB1FC9C-C1B3-4E57-82ED-6B4EB3BDFD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5B4E17E3-C17D-4116-8184-FB3AB4E1A581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1CF27B0E-1027-4419-BEEC-551758462B63}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="Slicer_Category">#N/A</definedName>
+    <definedName name="Slicer_Region">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
     <pivotCache cacheId="6" r:id="rId2"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId3"/>
+        <x14:slicerCache r:id="rId4"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="30">
   <si>
     <t>Order ID</t>
   </si>
@@ -97,18 +112,6 @@
     <t>Sum of Sales</t>
   </si>
   <si>
-    <t>Feb</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>Jul</t>
-  </si>
-  <si>
-    <t>Sep</t>
-  </si>
-  <si>
     <t>Jan</t>
   </si>
   <si>
@@ -124,14 +127,14 @@
     <t>Oct</t>
   </si>
   <si>
-    <t>Mar</t>
+    <t xml:space="preserve">Total Sales </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,8 +269,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -447,8 +457,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -563,6 +579,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -608,7 +650,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -617,6 +659,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1520,37 +1568,22 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>KPI!$L$2:$L$12</c:f>
+              <c:f>KPI!$L$2:$L$7</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Jan</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Feb</c:v>
+                  <c:v>Apr</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Mar</c:v>
+                  <c:v>Jun</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Apr</c:v>
+                  <c:v>Aug</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>May</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Jun</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Jul</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Aug</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Sep</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>Oct</c:v>
                 </c:pt>
               </c:strCache>
@@ -1558,39 +1591,24 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KPI!$M$2:$M$12</c:f>
+              <c:f>KPI!$M$2:$M$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>52000</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63000</c:v>
+                  <c:v>55000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17500</c:v>
+                  <c:v>3200</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>59500</c:v>
+                  <c:v>58000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13800</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>65200</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>19800</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>60200</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>32200</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>18400</c:v>
+                  <c:v>2900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3586,6 +3604,162 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>45721</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Category">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC0513BA-987D-8D6E-AAC4-015115B582C5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Category"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12054840" y="1"/>
+              <a:ext cx="1828800" cy="1691640"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Region">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E49E9FC5-2029-F574-19C4-B389573EDBF5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Region"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9235440" y="1"/>
+              <a:ext cx="1828800" cy="1981200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4053,7 +4227,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="139557185"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -4246,7 +4420,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A45B3224-92A1-441B-B04F-0B4385BE255C}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="L1:M12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="L1:M7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -4281,10 +4455,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
+        <item h="1" x="0"/>
+        <item h="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4687,33 +4861,18 @@
     <field x="8"/>
     <field x="7"/>
   </rowFields>
-  <rowItems count="11">
+  <rowItems count="6">
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i>
       <x v="4"/>
     </i>
     <i>
-      <x v="5"/>
-    </i>
-    <i>
       <x v="6"/>
     </i>
     <i>
-      <x v="7"/>
-    </i>
-    <i>
       <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
     </i>
     <i>
       <x v="10"/>
@@ -6214,6 +6373,47 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Category" xr10:uid="{08A41D83-1F0B-428B-97D7-9463BEA10049}" sourceName="Category">
+  <pivotTables>
+    <pivotTable tabId="1" name="PivotTable5"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="139557185">
+      <items count="2">
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Region" xr10:uid="{3967C300-84DC-465F-A0F6-21469F88C069}" sourceName="Region">
+  <pivotTables>
+    <pivotTable tabId="1" name="PivotTable5"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="139557185">
+      <items count="4">
+        <i x="2"/>
+        <i x="1" s="1"/>
+        <i x="0"/>
+        <i x="3"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Category" xr10:uid="{E9A30E40-A67B-466D-9215-0B586BD255A5}" cache="Slicer_Category" caption="Category" rowHeight="247650"/>
+  <slicer name="Region" xr10:uid="{BF22E1CB-F2DC-4295-B66B-394DC93CE49C}" cache="Slicer_Region" caption="Region" rowHeight="247650"/>
+</slicers>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6531,7 +6731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43D530B-BEF3-47E4-BBA7-14928D42F68C}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
@@ -6545,9 +6745,12 @@
     <col min="10" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.6640625" customWidth="1"/>
+    <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -6582,7 +6785,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6611,13 +6814,13 @@
         <v>30100</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M2" s="4">
-        <v>52000</v>
+        <v>2000</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6646,13 +6849,13 @@
         <v>371500</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3" s="4">
-        <v>63000</v>
+        <v>55000</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6681,13 +6884,13 @@
         <v>401600</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="M4" s="4">
-        <v>17500</v>
+        <v>3200</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6710,13 +6913,13 @@
         <v>2</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M5" s="4">
-        <v>59500</v>
+        <v>58000</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6745,13 +6948,13 @@
         <v>23</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M6" s="4">
-        <v>13800</v>
+        <v>2900</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6780,13 +6983,13 @@
         <v>35200</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M7" s="4">
-        <v>65200</v>
+        <v>121100</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6814,14 +7017,8 @@
       <c r="J8" s="4">
         <v>121100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" s="4">
-        <v>19800</v>
-      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6849,14 +7046,8 @@
       <c r="J9" s="4">
         <v>196700</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" s="4">
-        <v>60200</v>
-      </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6884,14 +7075,8 @@
       <c r="J10" s="4">
         <v>48600</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="4">
-        <v>32200</v>
-      </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6919,14 +7104,8 @@
       <c r="J11" s="4">
         <v>401600</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" s="4">
-        <v>18400</v>
-      </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6948,14 +7127,8 @@
       <c r="G12">
         <v>3</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="4">
-        <v>401600</v>
-      </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6984,7 +7157,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -7012,8 +7185,15 @@
       <c r="J14" s="4">
         <v>8700</v>
       </c>
+      <c r="R14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S14" s="7">
+        <f>SUM(F2:F21)</f>
+        <v>401600</v>
+      </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -7042,7 +7222,7 @@
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -7069,6 +7249,10 @@
       </c>
       <c r="J16" s="4">
         <v>285000</v>
+      </c>
+      <c r="R16" t="str">
+        <f>_xlfn.CONCAT(R14,S14)</f>
+        <v>Total Sales 401600</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -7228,5 +7412,12 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
   <drawing r:id="rId6"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId7"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/KPI.xlsx
+++ b/KPI.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5B4E17E3-C17D-4116-8184-FB3AB4E1A581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A6126DE4-5AB8-44B6-A508-5F6C56F09B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1CF27B0E-1027-4419-BEEC-551758462B63}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1CF27B0E-1027-4419-BEEC-551758462B63}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Category">#N/A</definedName>
@@ -21,13 +22,13 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId2"/>
+    <pivotCache cacheId="6" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId3"/>
         <x14:slicerCache r:id="rId4"/>
+        <x14:slicerCache r:id="rId5"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="41">
   <si>
     <t>Order ID</t>
   </si>
@@ -112,6 +113,18 @@
     <t>Sum of Sales</t>
   </si>
   <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
     <t>Jan</t>
   </si>
   <si>
@@ -127,14 +140,35 @@
     <t>Oct</t>
   </si>
   <si>
+    <t>Mar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total Sales </t>
+  </si>
+  <si>
+    <t>Total Orders</t>
+  </si>
+  <si>
+    <t>Average Sales</t>
+  </si>
+  <si>
+    <t>Electronics contributes majority of revenue</t>
+  </si>
+  <si>
+    <t>South region performs best</t>
+  </si>
+  <si>
+    <t>Sales dip observed in March</t>
+  </si>
+  <si>
+    <t>Accessories category needs improvement</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,6 +306,13 @@
     <font>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -650,7 +691,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -664,6 +705,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -710,7 +754,28 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -738,7 +803,7 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[KPI.xlsx]KPI!PivotTable3</c:name>
-    <c:fmtId val="0"/>
+    <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -775,6 +840,118 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent1"/>
@@ -903,7 +1080,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9E58-4FA5-8BA2-3297E2180699}"/>
+              <c16:uniqueId val="{00000000-93D5-4821-87C8-758BA5FF08C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1141,7 +1318,7 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[KPI.xlsx]KPI!PivotTable1</c:name>
-    <c:fmtId val="12"/>
+    <c:fmtId val="15"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -1234,6 +1411,178 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -1267,6 +1616,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-39C9-4286-9E10-ED9948360A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1282,6 +1636,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-39C9-4286-9E10-ED9948360A8E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -1314,7 +1673,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-075F-4CBF-83D7-211F64FDFE72}"/>
+              <c16:uniqueId val="{00000004-39C9-4286-9E10-ED9948360A8E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1443,7 +1802,7 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[KPI.xlsx]KPI!PivotTable5</c:name>
-    <c:fmtId val="3"/>
+    <c:fmtId val="6"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -1480,6 +1839,124 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
         <c:spPr>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
@@ -1568,22 +2045,37 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>KPI!$L$2:$L$7</c:f>
+              <c:f>KPI!$L$2:$L$12</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>Jan</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Apr</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Jun</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>Aug</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Oct</c:v>
                 </c:pt>
               </c:strCache>
@@ -1591,24 +2083,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KPI!$M$2:$M$7</c:f>
+              <c:f>KPI!$M$2:$M$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2000</c:v>
+                  <c:v>52000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55000</c:v>
+                  <c:v>63000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3200</c:v>
+                  <c:v>17500</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>58000</c:v>
+                  <c:v>59500</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2900</c:v>
+                  <c:v>13800</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>65200</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19800</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>60200</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32200</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18400</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1616,7 +2123,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-073D-413B-8B78-06BAD4CCCF72}"/>
+              <c16:uniqueId val="{00000000-7342-4F62-B44A-149C21CD2825}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3501,26 +4008,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>179070</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1089660</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD81DADA-26F8-17F1-C4D2-F578E3CCEB6E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD20EDE-56D8-4B13-B2E0-B090E6FDA3EA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3536,15 +4045,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3552,11 +4061,13 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57B1C345-F5F4-A00F-4F64-83C0FDADF27A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECE1FCBC-C052-404D-A542-855B1AF77D39}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3572,27 +4083,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>125730</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1082040</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EC9EB41-41AD-1273-1047-75C71F14D90E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BA9A062-FC03-4A85-BC58-FC319FAD575A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3608,25 +4121,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>60960</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>556260</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>45721</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1219200</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="5" name="Category">
+            <xdr:cNvPr id="5" name="Region">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC0513BA-987D-8D6E-AAC4-015115B582C5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F22DF9D0-2BBA-4186-AFF2-09113CE2C99D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3638,7 +4151,7 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Category"/>
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Region"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
@@ -3653,8 +4166,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12054840" y="1"/>
-              <a:ext cx="1828800" cy="1691640"/>
+              <a:off x="3810000" y="3870476"/>
+              <a:ext cx="1823962" cy="1701437"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3686,25 +4199,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>556260</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>22859</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="6" name="Region">
+            <xdr:cNvPr id="6" name="Category">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E49E9FC5-2029-F574-19C4-B389573EDBF5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D98108A-976F-4D70-8B91-C484AC39C735}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3716,7 +4229,7 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Region"/>
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Category"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
@@ -3731,8 +4244,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9235440" y="1"/>
-              <a:ext cx="1828800" cy="1981200"/>
+              <a:off x="6289524" y="3870476"/>
+              <a:ext cx="1814286" cy="1111431"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4419,8 +4932,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A45B3224-92A1-441B-B04F-0B4385BE255C}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="L1:M7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A45B3224-92A1-441B-B04F-0B4385BE255C}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="L1:M12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -4455,10 +4968,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="3"/>
+        <item x="0"/>
+        <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4861,18 +5374,33 @@
     <field x="8"/>
     <field x="7"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="11">
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i>
       <x v="4"/>
     </i>
     <i>
+      <x v="5"/>
+    </i>
+    <i>
       <x v="6"/>
     </i>
     <i>
+      <x v="7"/>
+    </i>
+    <i>
       <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
     </i>
     <i>
       <x v="10"/>
@@ -4887,8 +5415,17 @@
   <dataFields count="1">
     <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5412,7 +5949,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C07ABC0E-BAEE-492F-BAA4-8DF4097193F5}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C07ABC0E-BAEE-492F-BAA4-8DF4097193F5}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="I6:J11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -5876,8 +6413,17 @@
   <dataFields count="1">
     <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5900,7 +6446,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B1D6B85-ABC5-4AD5-BEE7-AEC5263673BC}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B1D6B85-ABC5-4AD5-BEE7-AEC5263673BC}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16">
   <location ref="I1:J4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -6350,12 +6896,45 @@
   <dataFields count="1">
     <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="4">
     <chartFormat chart="12" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -6374,7 +6953,25 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Category" xr10:uid="{08A41D83-1F0B-428B-97D7-9463BEA10049}" sourceName="Category">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Region" xr10:uid="{E8861855-95B6-464B-A57C-AD940BD2A1CA}" sourceName="Region">
+  <pivotTables>
+    <pivotTable tabId="1" name="PivotTable5"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="139557185">
+      <items count="4">
+        <i x="2" s="1"/>
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="3" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Category" xr10:uid="{6FE3C26B-8976-4453-AFDC-25B51470945A}" sourceName="Category">
   <pivotTables>
     <pivotTable tabId="1" name="PivotTable5"/>
   </pivotTables>
@@ -6389,28 +6986,10 @@
 </slicerCacheDefinition>
 </file>
 
-<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Region" xr10:uid="{3967C300-84DC-465F-A0F6-21469F88C069}" sourceName="Region">
-  <pivotTables>
-    <pivotTable tabId="1" name="PivotTable5"/>
-  </pivotTables>
-  <data>
-    <tabular pivotCacheId="139557185">
-      <items count="4">
-        <i x="2"/>
-        <i x="1" s="1"/>
-        <i x="0"/>
-        <i x="3"/>
-      </items>
-    </tabular>
-  </data>
-</slicerCacheDefinition>
-</file>
-
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Category" xr10:uid="{E9A30E40-A67B-466D-9215-0B586BD255A5}" cache="Slicer_Category" caption="Category" rowHeight="247650"/>
-  <slicer name="Region" xr10:uid="{BF22E1CB-F2DC-4295-B66B-394DC93CE49C}" cache="Slicer_Region" caption="Region" rowHeight="247650"/>
+  <slicer name="Region" xr10:uid="{214B7258-85CB-4A2D-BDBC-7B6D962C8E45}" cache="Slicer_Region" caption="Region" rowHeight="247650"/>
+  <slicer name="Category" xr10:uid="{7DFB0031-91CE-45BE-B42A-9C2BF958163B}" cache="Slicer_Category" caption="Category" rowHeight="247650"/>
 </slicers>
 </file>
 
@@ -6731,7 +7310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43D530B-BEF3-47E4-BBA7-14928D42F68C}">
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
@@ -6746,11 +7325,11 @@
     <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="6.6640625" customWidth="1"/>
-    <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -6785,7 +7364,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6814,13 +7393,13 @@
         <v>30100</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M2" s="4">
-        <v>2000</v>
+        <v>52000</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6849,13 +7428,13 @@
         <v>371500</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M3" s="4">
-        <v>55000</v>
+        <v>63000</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6884,13 +7463,13 @@
         <v>401600</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="M4" s="4">
-        <v>3200</v>
+        <v>17500</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6913,13 +7492,13 @@
         <v>2</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M5" s="4">
-        <v>58000</v>
+        <v>59500</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6948,13 +7527,13 @@
         <v>23</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M6" s="4">
-        <v>2900</v>
+        <v>13800</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6983,13 +7562,13 @@
         <v>35200</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M7" s="4">
-        <v>121100</v>
+        <v>65200</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7017,8 +7596,14 @@
       <c r="J8" s="4">
         <v>121100</v>
       </c>
+      <c r="L8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="4">
+        <v>19800</v>
+      </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7046,8 +7631,14 @@
       <c r="J9" s="4">
         <v>196700</v>
       </c>
+      <c r="L9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9" s="4">
+        <v>60200</v>
+      </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -7075,8 +7666,14 @@
       <c r="J10" s="4">
         <v>48600</v>
       </c>
+      <c r="L10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="4">
+        <v>32200</v>
+      </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -7104,8 +7701,14 @@
       <c r="J11" s="4">
         <v>401600</v>
       </c>
+      <c r="L11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="4">
+        <v>18400</v>
+      </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -7127,8 +7730,14 @@
       <c r="G12">
         <v>3</v>
       </c>
+      <c r="L12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="4">
+        <v>401600</v>
+      </c>
     </row>
-    <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -7157,7 +7766,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -7185,15 +7794,8 @@
       <c r="J14" s="4">
         <v>8700</v>
       </c>
-      <c r="R14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S14" s="7">
-        <f>SUM(F2:F21)</f>
-        <v>401600</v>
-      </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -7222,7 +7824,7 @@
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -7249,10 +7851,6 @@
       </c>
       <c r="J16" s="4">
         <v>285000</v>
-      </c>
-      <c r="R16" t="str">
-        <f>_xlfn.CONCAT(R14,S14)</f>
-        <v>Total Sales 401600</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -7409,13 +8007,81 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>50000</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
-  <drawing r:id="rId6"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F160330-5328-4236-93C7-3E08C9F40F19}">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="80.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="7">
+        <f>SUM(KPI!F2:F21)</f>
+        <v>401600</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="7">
+        <f>COUNT(KPI!A2:A21)</f>
+        <v>20</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="7">
+        <f>AVERAGE(KPI!F2:F21)</f>
+        <v>20080</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="M4" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="M5" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="M6" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="M7" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId7"/>
+        <x14:slicer r:id="rId2"/>
       </x14:slicerList>
     </ext>
   </extLst>
